--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
@@ -564,42 +564,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -632,16 +632,16 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -663,37 +663,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -703,41 +703,41 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="Q3" t="n">
         <v>0.31</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
         <v>15</v>
@@ -762,42 +762,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -807,16 +807,16 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q4" t="n">
         <v>0.31</v>
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -861,32 +861,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -906,19 +906,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -960,84 +960,84 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0.42</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
         <v>10</v>
       </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V7" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1158,37 +1158,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1212,27 +1212,27 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
         <v>16</v>
@@ -1257,27 +1257,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,34 +1307,34 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,19 +1381,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>center</t>
@@ -1401,19 +1401,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="n">
         <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1455,52 +1455,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1509,30 +1509,30 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="Q11" t="n">
         <v>0.2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="U12" t="n">
-        <v>7</v>
-      </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1653,27 +1653,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1698,19 +1698,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>0.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1777,22 +1777,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P14" t="n">
         <v>0.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1823,13 +1823,13 @@
         <v>15</v>
       </c>
       <c r="U14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1851,84 +1851,84 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>0.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1950,37 +1950,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1995,19 +1995,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2018,13 +2018,13 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
         <v>17</v>
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -2148,42 +2148,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2216,16 +2216,16 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2247,57 +2247,57 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2308,23 +2308,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2346,42 +2346,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2445,37 +2445,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2485,41 +2485,41 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S21" t="n">
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
         <v>17</v>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,30 +2598,30 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0.27</v>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="W22" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -2643,22 +2643,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2742,47 +2742,47 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2792,34 +2792,34 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14</v>
+      </c>
+      <c r="W24" t="n">
         <v>10</v>
-      </c>
-      <c r="U24" t="n">
-        <v>7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2898,7 +2898,7 @@
         <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2909,13 +2909,13 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>6</v>
@@ -2940,84 +2940,84 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
         <v>0.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3039,52 +3039,52 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3093,30 +3093,30 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q27" t="n">
         <v>0.26</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S27" t="n">
         <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -3138,44 +3138,44 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>right</t>
@@ -3183,19 +3183,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V28" t="n">
+        <v>3</v>
+      </c>
+      <c r="W28" t="n">
         <v>4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -3237,84 +3237,84 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q29" t="n">
         <v>0.25</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S29" t="n">
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -3336,84 +3336,84 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -3435,42 +3435,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -3503,16 +3503,16 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -3534,42 +3534,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3579,19 +3579,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
         <v>10</v>
       </c>
-      <c r="U32" t="n">
-        <v>5</v>
-      </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3633,84 +3633,84 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q33" t="n">
         <v>0.47</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -3732,84 +3732,84 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" t="n">
         <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>9</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -3930,22 +3930,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3955,43 +3955,43 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4001,13 +4001,13 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
+        <v>9</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6</v>
+      </c>
+      <c r="W36" t="n">
         <v>8</v>
-      </c>
-      <c r="V36" t="n">
-        <v>17</v>
-      </c>
-      <c r="W36" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -4029,42 +4029,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4074,19 +4074,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P37" t="n">
         <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.2</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
         <v>4</v>
       </c>
-      <c r="U38" t="n">
-        <v>7</v>
-      </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -4227,27 +4227,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4272,19 +4272,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4351,43 +4351,43 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4397,13 +4397,13 @@
         <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -4425,84 +4425,84 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -4524,42 +4524,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4569,19 +4569,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P42" t="n">
         <v>0.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -4592,16 +4592,16 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
@@ -4623,84 +4623,84 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V43" t="n">
+        <v>5</v>
+      </c>
+      <c r="W43" t="n">
         <v>8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -4722,84 +4722,84 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q44" t="n">
         <v>0.42</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S44" t="n">
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -4821,32 +4821,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4871,34 +4871,34 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q45" t="n">
         <v>0.42</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
         <v>10</v>
       </c>
       <c r="W45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
@@ -4920,84 +4920,84 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P46" t="n">
         <v>0.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -5019,47 +5019,47 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5069,34 +5069,34 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -5118,17 +5118,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5138,19 +5138,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>flower</t>
@@ -5158,41 +5158,41 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S48" t="n">
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
         <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
         <v>6</v>
@@ -5217,22 +5217,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5242,22 +5242,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5267,18 +5267,18 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5288,13 +5288,13 @@
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V49" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W49" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -5316,84 +5316,84 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S50" t="n">
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="W50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -5415,42 +5415,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5460,19 +5460,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -5514,42 +5514,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5559,19 +5559,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
         <v>0.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V52" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -5613,57 +5613,57 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -5674,23 +5674,23 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S53" t="n">
         <v>14</v>
       </c>
       <c r="T53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V53" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -5712,37 +5712,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5773,20 +5773,20 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S54" t="n">
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U54" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W54" t="n">
         <v>15</v>
@@ -5811,42 +5811,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5879,16 +5879,16 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W55" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -5910,42 +5910,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5955,19 +5955,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -6009,47 +6009,47 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6059,34 +6059,34 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q57" t="n">
         <v>0.36</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S57" t="n">
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W57" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -6108,57 +6108,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -6169,23 +6169,23 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S58" t="n">
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
         <v>10</v>
       </c>
-      <c r="U58" t="n">
-        <v>5</v>
-      </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -6207,84 +6207,84 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q59" t="n">
         <v>0.47</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W59" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -6306,37 +6306,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6346,17 +6346,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -6367,20 +6367,20 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S60" t="n">
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U60" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
         <v>15</v>
@@ -6405,27 +6405,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6445,41 +6445,41 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W61" t="n">
         <v>5</v>
@@ -6504,22 +6504,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6529,43 +6529,43 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q62" t="n">
         <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6575,13 +6575,13 @@
         <v>2</v>
       </c>
       <c r="U62" t="n">
+        <v>9</v>
+      </c>
+      <c r="V62" t="n">
+        <v>15</v>
+      </c>
+      <c r="W62" t="n">
         <v>8</v>
-      </c>
-      <c r="V62" t="n">
-        <v>11</v>
-      </c>
-      <c r="W62" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -6702,84 +6702,84 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q64" t="n">
         <v>0.27</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>7</v>
+      </c>
+      <c r="U64" t="n">
         <v>4</v>
       </c>
-      <c r="U64" t="n">
-        <v>7</v>
-      </c>
       <c r="V64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6836,40 +6836,40 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S65" t="n">
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U65" t="n">
         <v>15</v>
@@ -6878,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P66" t="n">
         <v>0.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6971,13 +6971,13 @@
         <v>15</v>
       </c>
       <c r="U66" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V66" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -6999,84 +6999,84 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S67" t="n">
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -7098,39 +7098,39 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_24.jpg</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>phone</t>
@@ -7143,19 +7143,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -7166,13 +7166,13 @@
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U68" t="n">
+        <v>3</v>
+      </c>
+      <c r="V68" t="n">
         <v>6</v>
-      </c>
-      <c r="V68" t="n">
-        <v>4</v>
       </c>
       <c r="W68" t="n">
         <v>17</v>
@@ -7197,47 +7197,47 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7247,34 +7247,34 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S69" t="n">
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
@@ -7296,37 +7296,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7341,19 +7341,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7364,13 +7364,13 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U70" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
         <v>17</v>
@@ -7395,47 +7395,47 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7445,34 +7445,34 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" t="n">
         <v>9</v>
       </c>
-      <c r="U71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
-        <v>7</v>
-      </c>
       <c r="W71" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -7494,84 +7494,84 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q72" t="n">
         <v>0.47</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -7593,42 +7593,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -7661,16 +7661,16 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
+        <v>9</v>
+      </c>
+      <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
         <v>8</v>
       </c>
-      <c r="U73" t="n">
-        <v>5</v>
-      </c>
-      <c r="V73" t="n">
-        <v>17</v>
-      </c>
       <c r="W73" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -7692,27 +7692,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7737,16 +7737,16 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q74" t="n">
         <v>0.2</v>
@@ -7760,7 +7760,7 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U74" t="n">
         <v>2</v>
@@ -7769,7 +7769,7 @@
         <v>15</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7816,17 +7816,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7836,19 +7836,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7862,13 +7862,13 @@
         <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V75" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W75" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7890,47 +7890,47 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -7951,23 +7951,23 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S76" t="n">
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U76" t="n">
+        <v>4</v>
+      </c>
+      <c r="V76" t="n">
+        <v>15</v>
+      </c>
+      <c r="W76" t="n">
         <v>7</v>
-      </c>
-      <c r="V76" t="n">
-        <v>11</v>
-      </c>
-      <c r="W76" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -7989,47 +7989,47 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8039,34 +8039,34 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U77" t="n">
+        <v>8</v>
+      </c>
+      <c r="V77" t="n">
         <v>3</v>
       </c>
-      <c r="V77" t="n">
-        <v>16</v>
-      </c>
       <c r="W77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,42 +8088,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8133,19 +8133,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>0.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8156,16 +8156,16 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -8187,47 +8187,47 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8237,34 +8237,34 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S79" t="n">
         <v>14</v>
       </c>
       <c r="T79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V79" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -8286,84 +8286,84 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S80" t="n">
         <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U80" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8420,49 +8420,49 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P81" t="n">
         <v>0.53</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S81" t="n">
         <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V81" t="n">
         <v>2</v>
       </c>
       <c r="W81" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -8484,47 +8484,47 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8534,34 +8534,34 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S82" t="n">
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -8583,42 +8583,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8628,19 +8628,19 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P83" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -8651,16 +8651,16 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
@@ -8682,42 +8682,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
+        <v>5</v>
+      </c>
+      <c r="U84" t="n">
         <v>10</v>
       </c>
-      <c r="U84" t="n">
-        <v>5</v>
-      </c>
       <c r="V84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -8781,52 +8781,52 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_34.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8835,30 +8835,30 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S85" t="n">
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U85" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W85" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -8880,44 +8880,44 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>center</t>
@@ -8925,19 +8925,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -8948,16 +8948,16 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V86" t="n">
         <v>7</v>
       </c>
       <c r="W86" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -8979,27 +8979,27 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_32.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="Q87" t="n">
         <v>0.2</v>
@@ -9047,16 +9047,16 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9103,22 +9103,22 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9128,18 +9128,18 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9149,13 +9149,13 @@
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V88" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="W88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -9177,84 +9177,84 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_22.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S89" t="n">
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>9</v>
+      </c>
+      <c r="U89" t="n">
+        <v>7</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4</v>
+      </c>
+      <c r="W89" t="n">
         <v>8</v>
-      </c>
-      <c r="U89" t="n">
-        <v>4</v>
-      </c>
-      <c r="V89" t="n">
-        <v>16</v>
-      </c>
-      <c r="W89" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -9276,42 +9276,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_01.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_03.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_40.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q90" t="n">
         <v>0.4</v>
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
+        <v>7</v>
+      </c>
+      <c r="U90" t="n">
         <v>4</v>
       </c>
-      <c r="U90" t="n">
-        <v>7</v>
-      </c>
       <c r="V90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -9375,27 +9375,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/car/car_41.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9420,16 +9420,16 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q91" t="n">
         <v>0.53</v>
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
         <v>15</v>
       </c>
       <c r="V91" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -9474,22 +9474,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/key/key_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_24.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9499,14 +9499,14 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>bread</t>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9528,14 +9528,14 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -9545,10 +9545,10 @@
         <v>15</v>
       </c>
       <c r="U92" t="n">
+        <v>13</v>
+      </c>
+      <c r="V92" t="n">
         <v>16</v>
-      </c>
-      <c r="V92" t="n">
-        <v>1</v>
       </c>
       <c r="W92" t="n">
         <v>3</v>
@@ -9573,42 +9573,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9618,16 +9618,16 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="Q93" t="n">
         <v>0.2</v>
@@ -9641,16 +9641,16 @@
         <v>2</v>
       </c>
       <c r="T93" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U93" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
@@ -9672,42 +9672,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q94" t="n">
         <v>0.36</v>
@@ -9740,16 +9740,16 @@
         <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -9771,37 +9771,37 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9816,19 +9816,19 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -9839,13 +9839,13 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W95" t="n">
         <v>17</v>
@@ -9870,84 +9870,84 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S96" t="n">
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W96" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
@@ -9969,32 +9969,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -10019,34 +10019,34 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q97" t="n">
         <v>0.47</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S97" t="n">
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V97" t="n">
         <v>10</v>
       </c>
       <c r="W97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98">
@@ -10068,37 +10068,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -10118,31 +10118,31 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S98" t="n">
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V98" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W98" t="n">
         <v>3</v>
@@ -10167,52 +10167,52 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10221,30 +10221,30 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S99" t="n">
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="W99" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
@@ -10266,27 +10266,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_24.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -10320,30 +10320,30 @@
         </is>
       </c>
       <c r="P100" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q100" t="n">
         <v>0.33</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S100" t="n">
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
         <v>2</v>
       </c>
       <c r="V100" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="W100" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -10365,22 +10365,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10390,22 +10390,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -10415,18 +10415,18 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10436,13 +10436,13 @@
         <v>2</v>
       </c>
       <c r="U101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V101" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="W101" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -10464,37 +10464,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_03.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -10521,24 +10521,24 @@
         <v>0.53</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S102" t="n">
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V102" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W102" t="n">
         <v>1</v>
@@ -10563,84 +10563,84 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_16.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_17.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_25.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="Q103" t="n">
         <v>0.27</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S103" t="n">
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U103" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V103" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -10662,84 +10662,84 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/car/car_35.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_07.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P104" t="n">
         <v>0.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S104" t="n">
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -10761,84 +10761,84 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_43.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_12.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/key/key_21.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_32.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S105" t="n">
         <v>14</v>
       </c>
       <c r="T105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V105" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0.2</v>
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>18</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -703,28 +703,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0.31</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,7 +737,7 @@
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>17</v>
@@ -802,17 +802,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,38 +891,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,22 +990,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1034,10 +1034,10 @@
         <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,38 +1089,38 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>9</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1203,19 +1203,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,28 +1297,28 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q9" t="n">
         <v>0.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1331,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
         <v>5</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0.33</v>
@@ -1529,7 +1529,7 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
         <v>6</v>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1584,22 +1584,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1628,10 +1628,10 @@
         <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1698,19 +1698,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>0.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,38 +1782,38 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1826,10 +1826,10 @@
         <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1995,19 +1995,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2099,18 +2099,18 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,10 +2123,10 @@
         <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,17 +2178,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,18 +2198,18 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2396,18 +2396,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,10 +2420,10 @@
         <v>8</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q22" t="n">
         <v>0.2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>10</v>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         <v>9</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q24" t="n">
         <v>0.2</v>
@@ -2816,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2886,19 +2886,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2994,14 +2994,14 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0.27</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3014,7 +3014,7 @@
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
         <v>2</v>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,22 +3069,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3093,14 +3093,14 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>13</v>
       </c>
       <c r="V27" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3173,33 +3173,33 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P28" t="n">
         <v>0.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3215,7 +3215,7 @@
         <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3287,18 +3287,18 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P29" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3314,7 +3314,7 @@
         <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3485,18 +3485,18 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3509,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>0.53</v>
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
         <v>8</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,22 +3861,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3885,14 +3885,14 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.58</v>
+        <v>0.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,22 +3960,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3984,14 +3984,14 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>5</v>
       </c>
       <c r="V36" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,38 +4059,38 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4103,10 +4103,10 @@
         <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4163,33 +4163,33 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
         <v>0.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -4205,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,22 +4257,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4281,14 +4281,14 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,10 +4301,10 @@
         <v>17</v>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="W39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,38 +4455,38 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>16</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4569,19 +4569,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P42" t="n">
         <v>0.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>5</v>
       </c>
       <c r="W42" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4673,18 +4673,18 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,10 +4697,10 @@
         <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4752,17 +4752,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4772,18 +4772,18 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4796,10 +4796,10 @@
         <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4851,38 +4851,38 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,10 +4895,10 @@
         <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5064,19 +5064,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         <v>1</v>
       </c>
       <c r="V47" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5148,17 +5148,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5168,18 +5168,18 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,10 +5192,10 @@
         <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W48" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5262,19 +5262,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         <v>9</v>
       </c>
       <c r="V49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W49" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5361,19 +5361,19 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5390,10 +5390,10 @@
         <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5559,16 +5559,16 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0.27</v>
@@ -5588,7 +5588,7 @@
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W52" t="n">
         <v>2</v>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5663,18 +5663,18 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5687,10 +5687,10 @@
         <v>13</v>
       </c>
       <c r="V53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5742,38 +5742,38 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,10 +5786,10 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,38 +5841,38 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5885,10 +5885,10 @@
         <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5940,38 +5940,38 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5984,10 +5984,10 @@
         <v>7</v>
       </c>
       <c r="V56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6083,10 +6083,10 @@
         <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W57" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6153,16 +6153,16 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q58" t="n">
         <v>0.42</v>
@@ -6182,7 +6182,7 @@
         <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
         <v>18</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6247,28 +6247,28 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q59" t="n">
         <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6281,7 +6281,7 @@
         <v>9</v>
       </c>
       <c r="V59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W59" t="n">
         <v>17</v>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6360,14 +6360,14 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6380,10 +6380,10 @@
         <v>10</v>
       </c>
       <c r="V60" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,38 +6435,38 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6479,10 +6479,10 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q62" t="n">
         <v>0.2</v>
@@ -6578,7 +6578,7 @@
         <v>5</v>
       </c>
       <c r="V62" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W62" t="n">
         <v>9</v>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,38 +6633,38 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -6677,10 +6677,10 @@
         <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W63" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6732,17 +6732,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,18 +6752,18 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6776,10 +6776,10 @@
         <v>8</v>
       </c>
       <c r="V64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6846,16 +6846,16 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q65" t="n">
         <v>0.33</v>
@@ -6875,7 +6875,7 @@
         <v>17</v>
       </c>
       <c r="V65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W65" t="n">
         <v>10</v>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6974,10 +6974,10 @@
         <v>18</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7044,16 +7044,16 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
@@ -7073,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W67" t="n">
         <v>13</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,38 +7128,38 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>6</v>
       </c>
       <c r="V68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W68" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7242,19 +7242,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
         <v>3</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7336,28 +7336,28 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q70" t="n">
         <v>0.36</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -7370,7 +7370,7 @@
         <v>5</v>
       </c>
       <c r="V70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
         <v>13</v>
@@ -7435,17 +7435,17 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S71" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7544,18 +7544,18 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P72" t="n">
         <v>0.75</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7571,7 +7571,7 @@
         <v>2</v>
       </c>
       <c r="W72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7623,22 +7623,22 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7647,14 +7647,14 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7667,10 +7667,10 @@
         <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="W73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7746,14 +7746,14 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7766,10 +7766,10 @@
         <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="W74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7836,19 +7836,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7865,10 +7865,10 @@
         <v>9</v>
       </c>
       <c r="V75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,38 +8019,38 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -8063,10 +8063,10 @@
         <v>4</v>
       </c>
       <c r="V77" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8118,38 +8118,38 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -8162,10 +8162,10 @@
         <v>15</v>
       </c>
       <c r="V78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,38 +8217,38 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>13</v>
       </c>
       <c r="V79" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="W79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8326,28 +8326,28 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -8360,7 +8360,7 @@
         <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W80" t="n">
         <v>18</v>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8415,38 +8415,38 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,10 +8459,10 @@
         <v>3</v>
       </c>
       <c r="V81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W81" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_11.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8519,17 +8519,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8541,11 +8541,11 @@
         <v>0.47</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8561,7 +8561,7 @@
         <v>4</v>
       </c>
       <c r="W82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8613,22 +8613,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8637,14 +8637,14 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -8657,10 +8657,10 @@
         <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W83" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -8821,17 +8821,17 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/hand/hand_29.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8934,10 +8934,10 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -8954,10 +8954,10 @@
         <v>10</v>
       </c>
       <c r="V86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W86" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/phone/phone_11.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -9053,10 +9053,10 @@
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="W87" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/hammer/hammer_02.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9108,22 +9108,22 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -9132,14 +9132,14 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9152,10 +9152,10 @@
         <v>5</v>
       </c>
       <c r="V88" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="W88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_29.jpg</t>
+          <t>stimuli/glasses/glasses_34.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,38 +9207,38 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -9251,10 +9251,10 @@
         <v>4</v>
       </c>
       <c r="V89" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W89" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -9326,18 +9326,18 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -9350,10 +9350,10 @@
         <v>8</v>
       </c>
       <c r="V90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/key/key_23.jpg</t>
+          <t>stimuli/lamp/lamp_12.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9405,38 +9405,38 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9449,10 +9449,10 @@
         <v>17</v>
       </c>
       <c r="V91" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/key/key_23.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9519,19 +9519,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -9548,10 +9548,10 @@
         <v>18</v>
       </c>
       <c r="V92" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W92" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9627,7 +9627,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="Q93" t="n">
         <v>0.2</v>
@@ -9647,7 +9647,7 @@
         <v>16</v>
       </c>
       <c r="V93" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W93" t="n">
         <v>13</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9726,14 +9726,14 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="Q94" t="n">
         <v>0.31</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9746,7 +9746,7 @@
         <v>6</v>
       </c>
       <c r="V94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W94" t="n">
         <v>15</v>
@@ -9781,12 +9781,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_49.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9801,38 +9801,38 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -9845,10 +9845,10 @@
         <v>3</v>
       </c>
       <c r="V95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W95" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_49.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9900,38 +9900,38 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -9944,10 +9944,10 @@
         <v>5</v>
       </c>
       <c r="V96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W96" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9999,38 +9999,38 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -10043,10 +10043,10 @@
         <v>10</v>
       </c>
       <c r="V97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10098,38 +10098,38 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -10142,10 +10142,10 @@
         <v>8</v>
       </c>
       <c r="V98" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W98" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_27.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,38 +10197,38 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -10241,10 +10241,10 @@
         <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W99" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/hammer/hammer_35.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/jacket/jacket_29.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10296,38 +10296,38 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -10340,10 +10340,10 @@
         <v>2</v>
       </c>
       <c r="V100" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/guitar/guitar_27.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_38.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,22 +10395,22 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10419,14 +10419,14 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10439,10 +10439,10 @@
         <v>9</v>
       </c>
       <c r="V101" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -10538,10 +10538,10 @@
         <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="W102" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
+          <t>stimuli/ball/ball_37.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10593,38 +10593,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -10637,10 +10637,10 @@
         <v>4</v>
       </c>
       <c r="V103" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="W103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -10672,12 +10672,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_37.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10692,38 +10692,38 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10736,10 +10736,10 @@
         <v>15</v>
       </c>
       <c r="V104" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="W104" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/hand/hand_38.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/glasses/glasses_26.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10791,38 +10791,38 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -10835,10 +10835,10 @@
         <v>13</v>
       </c>
       <c r="V105" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W105" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_12.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
         <v>18</v>
@@ -668,12 +668,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -734,10 +734,10 @@
         <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
         <v>17</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -830,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
         <v>7</v>
@@ -965,12 +965,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_23.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_23.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_42.jpg</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_23.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1127,16 +1127,16 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1427,13 +1427,13 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V10" t="n">
         <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>stimuli/house/house_42.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_12.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_12.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_08.jpg</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,16 +1523,16 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
         <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
       </c>
       <c r="V11" t="n">
         <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1622,7 +1622,7 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
         <v>8</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1727,10 +1727,10 @@
         <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
         <v>15</v>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
         <v>13</v>
@@ -2049,14 +2049,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_38.jpg</t>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2117,10 +2117,10 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
         <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2216,10 +2216,10 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V18" t="n">
         <v>2</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,7 +2315,7 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U19" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
         <v>18</v>
       </c>
       <c r="W19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2420,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
         <v>13</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2519,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
         <v>18</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2618,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W22" t="n">
         <v>10</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2714,7 +2714,7 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>7</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2810,7 +2810,7 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
         <v>7</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2912,13 +2912,13 @@
         <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V25" t="n">
         <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3008,13 +3008,13 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
         <v>2</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3113,7 +3113,7 @@
         <v>13</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
         <v>18</v>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3308,10 +3308,10 @@
         <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W29" t="n">
         <v>17</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3404,7 +3404,7 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
         <v>7</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W31" t="n">
         <v>15</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
         <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3800,7 +3800,7 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
         <v>10</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3908,7 +3908,7 @@
         <v>7</v>
       </c>
       <c r="W35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4001,13 +4001,13 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V36" t="n">
         <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -4029,14 +4029,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>stimuli/house/house_42.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_23.jpg</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_12.jpg</t>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4097,10 +4097,10 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
+        <v>9</v>
+      </c>
+      <c r="U37" t="n">
         <v>5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>4</v>
       </c>
       <c r="V37" t="n">
         <v>14</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4196,7 +4196,7 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
         <v>8</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4304,7 +4304,7 @@
         <v>18</v>
       </c>
       <c r="W39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>16</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
         <v>13</v>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4595,10 +4595,10 @@
         <v>16</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
         <v>7</v>
@@ -4623,14 +4623,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>stimuli/jacket/jacket_29.jpg</t>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4691,10 +4691,10 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
         <v>6</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>10</v>
@@ -4722,19 +4722,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_27.jpg</t>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
+        <v>9</v>
+      </c>
+      <c r="V44" t="n">
         <v>5</v>
-      </c>
-      <c r="V44" t="n">
-        <v>4</v>
       </c>
       <c r="W44" t="n">
         <v>13</v>
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_29.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_38.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_29.jpg</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_38.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,7 +4889,7 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U45" t="n">
         <v>10</v>
@@ -4898,7 +4898,7 @@
         <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4997,7 +4997,7 @@
         <v>18</v>
       </c>
       <c r="W46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5195,7 +5195,7 @@
         <v>18</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5288,10 +5288,10 @@
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W49" t="n">
         <v>16</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5384,13 +5384,13 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
         <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W50" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5486,7 +5486,7 @@
         <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
         <v>13</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
@@ -5623,14 +5623,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_07.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>key</t>
@@ -5643,12 +5643,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5687,10 +5687,10 @@
         <v>13</v>
       </c>
       <c r="V53" t="n">
+        <v>6</v>
+      </c>
+      <c r="W53" t="n">
         <v>3</v>
-      </c>
-      <c r="W53" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W54" t="n">
         <v>18</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5882,7 +5882,7 @@
         <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V55" t="n">
         <v>1</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5978,7 +5978,7 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U56" t="n">
         <v>7</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6083,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W57" t="n">
         <v>17</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6179,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V58" t="n">
         <v>8</v>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6275,10 +6275,10 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
         <v>10</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6374,7 +6374,7 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
         <v>10</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6482,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -6509,19 +6509,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_08.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_42.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -6529,17 +6529,17 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6575,13 +6575,13 @@
         <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V62" t="n">
+        <v>6</v>
+      </c>
+      <c r="W62" t="n">
         <v>3</v>
-      </c>
-      <c r="W62" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>stimuli/house/house_42.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_34.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_34.jpg</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_08.jpg</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>9</v>
+      </c>
+      <c r="U63" t="n">
         <v>5</v>
-      </c>
-      <c r="U63" t="n">
-        <v>4</v>
       </c>
       <c r="V63" t="n">
         <v>18</v>
       </c>
       <c r="W63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,7 +6770,7 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
         <v>8</v>
@@ -6779,7 +6779,7 @@
         <v>14</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W67" t="n">
         <v>13</v>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7169,13 +7169,13 @@
         <v>16</v>
       </c>
       <c r="U68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="W68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -7197,19 +7197,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>stimuli/key/key_11.jpg</t>
@@ -7217,17 +7217,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7265,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
         <v>6</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>3</v>
-      </c>
-      <c r="V69" t="n">
-        <v>9</v>
       </c>
       <c r="W69" t="n">
         <v>15</v>
@@ -7296,12 +7296,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7364,10 +7364,10 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V70" t="n">
         <v>10</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7463,7 +7463,7 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U71" t="n">
         <v>10</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7670,7 +7670,7 @@
         <v>16</v>
       </c>
       <c r="W73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_36.jpg</t>
-        </is>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>ball</t>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7766,10 +7766,10 @@
         <v>2</v>
       </c>
       <c r="V74" t="n">
+        <v>3</v>
+      </c>
+      <c r="W74" t="n">
         <v>9</v>
-      </c>
-      <c r="W74" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7862,10 +7862,10 @@
         <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W75" t="n">
         <v>10</v>
@@ -7890,42 +7890,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_04.jpg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_35.jpg</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_26.jpg</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_35.jpg</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_26.jpg</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_36.jpg</t>
-        </is>
-      </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,7 +7958,7 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U76" t="n">
         <v>7</v>
@@ -7967,7 +7967,7 @@
         <v>18</v>
       </c>
       <c r="W76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8060,7 +8060,7 @@
         <v>7</v>
       </c>
       <c r="U77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V77" t="n">
         <v>16</v>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U78" t="n">
         <v>15</v>
@@ -8165,7 +8165,7 @@
         <v>18</v>
       </c>
       <c r="W78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W80" t="n">
         <v>18</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8456,7 +8456,7 @@
         <v>14</v>
       </c>
       <c r="U81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V81" t="n">
         <v>2</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U82" t="n">
         <v>7</v>
       </c>
       <c r="V82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W82" t="n">
         <v>18</v>
@@ -8687,19 +8687,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_23.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_23.jpg</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_23.jpg</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>ball</t>
@@ -8707,17 +8707,17 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8753,13 +8753,13 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V84" t="n">
         <v>15</v>
       </c>
       <c r="W84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8849,10 +8849,10 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U85" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V85" t="n">
         <v>14</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_42.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8948,7 +8948,7 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U86" t="n">
         <v>10</v>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9053,7 +9053,7 @@
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W87" t="n">
         <v>17</v>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_42.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9149,13 +9149,13 @@
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V88" t="n">
         <v>7</v>
       </c>
       <c r="W88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>stimuli/house/house_42.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_23.jpg</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_34.jpg</t>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9245,10 +9245,10 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>9</v>
+      </c>
+      <c r="U89" t="n">
         <v>5</v>
-      </c>
-      <c r="U89" t="n">
-        <v>4</v>
       </c>
       <c r="V89" t="n">
         <v>18</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,7 +9344,7 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U90" t="n">
         <v>8</v>
@@ -9353,7 +9353,7 @@
         <v>15</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9548,7 +9548,7 @@
         <v>18</v>
       </c>
       <c r="V92" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W92" t="n">
         <v>15</v>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>16</v>
       </c>
       <c r="V93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W93" t="n">
         <v>13</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -9743,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="U94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V94" t="n">
         <v>7</v>
@@ -9771,42 +9771,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_04.jpg</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9839,16 +9839,16 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
+        <v>4</v>
+      </c>
+      <c r="U95" t="n">
         <v>6</v>
       </c>
-      <c r="U95" t="n">
-        <v>3</v>
-      </c>
       <c r="V95" t="n">
+        <v>9</v>
+      </c>
+      <c r="W95" t="n">
         <v>5</v>
-      </c>
-      <c r="W95" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -9870,12 +9870,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_04.jpg</t>
+          <t>stimuli/flower/flower_07.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9938,10 +9938,10 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U96" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V96" t="n">
         <v>2</v>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10037,7 +10037,7 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U97" t="n">
         <v>10</v>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10142,7 +10142,7 @@
         <v>8</v>
       </c>
       <c r="V98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W98" t="n">
         <v>15</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_36.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10244,7 +10244,7 @@
         <v>16</v>
       </c>
       <c r="W99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10436,13 +10436,13 @@
         <v>2</v>
       </c>
       <c r="U101" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V101" t="n">
         <v>13</v>
       </c>
       <c r="W101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_04.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_07.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10532,13 +10532,13 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U102" t="n">
         <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W102" t="n">
         <v>8</v>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/dog/dog_36.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10634,7 +10634,7 @@
         <v>7</v>
       </c>
       <c r="U103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V103" t="n">
         <v>18</v>
@@ -10662,19 +10662,19 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_36.jpg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_11.jpg</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_11.jpg</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_07.jpg</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_38.jpg</t>
@@ -10682,17 +10682,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10730,13 +10730,13 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U104" t="n">
         <v>15</v>
       </c>
       <c r="V104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W104" t="n">
         <v>8</v>
